--- a/reports/Debug-snowbowl-20251230/Month to Date (Actual)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20251230/Month to Date (Actual)_Revenue.xlsx
@@ -61,13 +61,13 @@
     <t xml:space="preserve">T104                     </t>
   </si>
   <si>
+    <t xml:space="preserve">T103                     </t>
+  </si>
+  <si>
     <t xml:space="preserve">T100                     </t>
   </si>
   <si>
     <t xml:space="preserve">T257                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T103                     </t>
   </si>
   <si>
     <t>department</t>
@@ -542,7 +542,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="2">
-        <v>3220627.1700</v>
+        <v>204739.2900</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -556,7 +556,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="2">
-        <v>193.0400</v>
+        <v>3220627.1700</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -570,7 +570,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="2">
-        <v>204739.2900</v>
+        <v>193.0400</v>
       </c>
     </row>
     <row r="8" spans="1:4">
